--- a/regression_deneme/regression_with_nn/gaziemir_monthly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/gaziemir_monthly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>33.93127952068426</v>
+        <v>43.11676221641167</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>48.61923074510455</v>
+        <v>48.52276602177301</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>53.75693003276142</v>
+        <v>54.93844280031616</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>38.22479058455654</v>
+        <v>46.65444829321316</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>37.9734930548754</v>
+        <v>52.03753999038261</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>53</v>
       </c>
       <c r="D7" t="n">
-        <v>51.4584868130727</v>
+        <v>69.66390663074195</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>50.43909215521493</v>
+        <v>53.08894211596633</v>
       </c>
     </row>
   </sheetData>
